--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{33D7B264-E024-46AE-875B-F5C883B9D1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{33D7B264-E024-46AE-875B-F5C883B9D1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{637C540A-A232-4A62-B3C2-95F04CAAD9D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="135">
   <si>
     <t>Produto</t>
   </si>
@@ -349,9 +349,6 @@
   </si>
   <si>
     <t>TRANSFER 99-5-4 PARCIAL FILM - GRAPHITE</t>
-  </si>
-  <si>
-    <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
   </si>
   <si>
     <t>TRANSFER LAM LASER ROSE NEW 2</t>
@@ -886,10 +883,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -906,7 +903,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -923,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -940,7 +937,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -957,7 +954,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -974,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -991,7 +988,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1008,7 +1005,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1025,7 +1022,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1042,7 +1039,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1059,7 +1056,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1076,7 +1073,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1093,7 +1090,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1110,7 +1107,7 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1127,7 +1124,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1144,7 +1141,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1161,7 +1158,7 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1178,7 +1175,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1195,7 +1192,7 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1212,7 +1209,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1229,7 +1226,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1246,7 +1243,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1263,7 +1260,7 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1271,214 +1268,214 @@
         <v>4413</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="4">
+        <v>10.3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
         <v>128</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D24" s="3">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>4423</v>
+        <v>4413</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="C25" s="4">
-        <v>100</v>
+        <v>2515</v>
       </c>
       <c r="D25" s="3">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>4721</v>
+        <v>4423</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4">
-        <v>1701.5</v>
+        <v>100</v>
       </c>
       <c r="D26" s="3">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>4722</v>
+        <v>4721</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4">
-        <v>3883.5</v>
+        <v>1701.5</v>
       </c>
       <c r="D27" s="3">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>4723</v>
+        <v>4722</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>2974.5</v>
+        <v>3883.5</v>
       </c>
       <c r="D28" s="3">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>5024</v>
+        <v>4723</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4">
-        <v>3325.5</v>
+        <v>2974.5</v>
       </c>
       <c r="D29" s="3">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>5025</v>
+        <v>5024</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="4">
-        <v>3064.5</v>
+        <v>3325.5</v>
       </c>
       <c r="D30" s="3">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>5437</v>
+        <v>5025</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="4">
-        <v>70</v>
+        <v>3064.5</v>
       </c>
       <c r="D31" s="3">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>5861</v>
+        <v>5437</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4">
-        <v>328</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>5931</v>
+        <v>5861</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4">
-        <v>11</v>
+        <v>328</v>
       </c>
       <c r="D33" s="3">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>5932</v>
+        <v>5931</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="4">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="D34" s="3">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>6248</v>
+        <v>5932</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="4">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="D35" s="3">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>6560</v>
+        <v>6248</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="4">
-        <v>2083.5</v>
+        <v>350</v>
       </c>
       <c r="D36" s="3">
         <v>12</v>
@@ -1489,19 +1486,19 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>7425</v>
+        <v>6560</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="4">
-        <v>300</v>
+        <v>2083.5</v>
       </c>
       <c r="D37" s="3">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1512,30 +1509,30 @@
         <v>37</v>
       </c>
       <c r="C38" s="4">
-        <v>7588.78</v>
+        <v>300</v>
       </c>
       <c r="D38" s="3">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>7484</v>
+        <v>7425</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="C39" s="4">
-        <v>2594</v>
+        <v>7588.78</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1543,16 +1540,16 @@
         <v>7484</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C40" s="4">
-        <v>5000</v>
+        <v>1272</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1563,13 +1560,13 @@
         <v>38</v>
       </c>
       <c r="C41" s="4">
-        <v>3404.5</v>
+        <v>2404.5</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1580,13 +1577,13 @@
         <v>39</v>
       </c>
       <c r="C42" s="4">
-        <v>17480.5</v>
+        <v>15880.5</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1603,7 +1600,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1620,7 +1617,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1637,7 +1634,7 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1654,7 +1651,7 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1671,7 +1668,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1688,7 +1685,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1705,7 +1702,7 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1722,7 +1719,7 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1739,7 +1736,7 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1750,13 +1747,13 @@
         <v>49</v>
       </c>
       <c r="C52" s="4">
-        <v>1328.5</v>
+        <v>528.5</v>
       </c>
       <c r="D52" s="3">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1773,7 +1770,7 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1790,7 +1787,7 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1801,13 +1798,13 @@
         <v>52</v>
       </c>
       <c r="C55" s="4">
-        <v>435.5</v>
+        <v>125.5</v>
       </c>
       <c r="D55" s="3">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1818,13 +1815,13 @@
         <v>53</v>
       </c>
       <c r="C56" s="4">
-        <v>1499</v>
+        <v>1299</v>
       </c>
       <c r="D56" s="3">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1841,7 +1838,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1858,7 +1855,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1875,7 +1872,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1892,7 +1889,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1909,7 +1906,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1926,7 +1923,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1943,7 +1940,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1960,7 +1957,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1977,7 +1974,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1994,7 +1991,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2011,7 +2008,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2028,7 +2025,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2045,7 +2042,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2062,7 +2059,7 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2079,7 +2076,7 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2096,7 +2093,7 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2113,7 +2110,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2121,92 +2118,92 @@
         <v>10090</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C74" s="4">
-        <v>3250</v>
+        <v>7550</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>10090</v>
+        <v>10254</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="C75" s="4">
-        <v>4900</v>
+        <v>70</v>
       </c>
       <c r="D75" s="3">
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>10254</v>
+        <v>10318</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C76" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D76" s="3">
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>10318</v>
+        <v>10362</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C77" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D77" s="3">
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>10362</v>
+        <v>10692</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D78" s="3">
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>10692</v>
+        <v>10707</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C79" s="4">
         <v>3</v>
@@ -2215,15 +2212,15 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>10707</v>
+        <v>10725</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C80" s="4">
         <v>3</v>
@@ -2232,83 +2229,83 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>10725</v>
+        <v>10762</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C81" s="4">
-        <v>3</v>
+        <v>1376.8</v>
       </c>
       <c r="D81" s="3">
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>10762</v>
+        <v>10830</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C82" s="4">
-        <v>1376.8</v>
+        <v>3</v>
       </c>
       <c r="D82" s="3">
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>10830</v>
+        <v>10832</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C83" s="4">
-        <v>3</v>
+        <v>1015</v>
       </c>
       <c r="D83" s="3">
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>10832</v>
+        <v>10834</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C84" s="4">
-        <v>1015</v>
+        <v>5</v>
       </c>
       <c r="D84" s="3">
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>10834</v>
+        <v>10836</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C85" s="4">
         <v>5</v>
@@ -2317,100 +2314,100 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>10836</v>
+        <v>10936</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C86" s="4">
-        <v>5</v>
+        <v>1093.3499999999999</v>
       </c>
       <c r="D86" s="3">
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>10936</v>
+        <v>10937</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C87" s="4">
-        <v>1093.3499999999999</v>
+        <v>1183.5</v>
       </c>
       <c r="D87" s="3">
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>10937</v>
+        <v>10997</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C88" s="4">
-        <v>1183.5</v>
+        <v>188.5</v>
       </c>
       <c r="D88" s="3">
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>10997</v>
+        <v>10998</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C89" s="4">
-        <v>188.5</v>
+        <v>69.352999999999994</v>
       </c>
       <c r="D89" s="3">
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>10998</v>
+        <v>11003</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C90" s="4">
-        <v>69.352999999999994</v>
+        <v>5</v>
       </c>
       <c r="D90" s="3">
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>11003</v>
+        <v>11105</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C91" s="4">
         <v>5</v>
@@ -2419,83 +2416,83 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>11105</v>
+        <v>11106</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C92" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D92" s="3">
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>11106</v>
+        <v>11107</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C93" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D93" s="3">
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11107</v>
+        <v>11243</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C94" s="4">
-        <v>5</v>
+        <v>209</v>
       </c>
       <c r="D94" s="3">
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11243</v>
+        <v>11269</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C95" s="4">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11269</v>
+        <v>11316</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C96" s="4">
         <v>10</v>
@@ -2504,117 +2501,117 @@
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11316</v>
+        <v>11318</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C97" s="4">
-        <v>10</v>
+        <v>97.7</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11318</v>
+        <v>11362</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C98" s="4">
-        <v>97.7</v>
+        <v>5</v>
       </c>
       <c r="D98" s="3">
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>11362</v>
+        <v>11396</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C99" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>11396</v>
+        <v>11397</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C100" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D100" s="3">
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>11397</v>
+        <v>11444</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C101" s="4">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="D101" s="3">
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>11444</v>
+        <v>12497</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C102" s="4">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="D102" s="3">
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>12497</v>
+        <v>12498</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C103" s="4">
         <v>5</v>
@@ -2623,15 +2620,15 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>12498</v>
+        <v>12499</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C104" s="4">
         <v>5</v>
@@ -2640,15 +2637,15 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>12499</v>
+        <v>12501</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C105" s="4">
         <v>5</v>
@@ -2657,15 +2654,15 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>12501</v>
+        <v>12503</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C106" s="4">
         <v>5</v>
@@ -2674,15 +2671,15 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>12503</v>
+        <v>12504</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
@@ -2691,86 +2688,86 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>12504</v>
+        <v>12514</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C108" s="4">
-        <v>5</v>
+        <v>1200.0999999999999</v>
       </c>
       <c r="D108" s="3">
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>12514</v>
+        <v>12515</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C109" s="4">
-        <v>1300.0999999999999</v>
+        <v>5480</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>12515</v>
+        <v>12516</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="C110" s="4">
-        <v>6480</v>
+        <v>2364.6</v>
       </c>
       <c r="D110" s="3">
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>12516</v>
+        <v>12517</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C111" s="4">
-        <v>2464.6</v>
+        <v>740.4</v>
       </c>
       <c r="D111" s="3">
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>12517</v>
+        <v>12673</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C112" s="4">
-        <v>840.4</v>
+        <v>5</v>
       </c>
       <c r="D112" s="3">
         <v>12</v>
@@ -2781,47 +2778,47 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>12518</v>
+        <v>13150</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C113" s="4">
-        <v>578.5</v>
+        <v>337.2</v>
       </c>
       <c r="D113" s="3">
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>12673</v>
+        <v>14365</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C114" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D114" s="3">
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>13150</v>
+        <v>14366</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C115" s="4">
-        <v>437.2</v>
+        <v>2</v>
       </c>
       <c r="D115" s="3">
         <v>12</v>
@@ -2832,10 +2829,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>14365</v>
+        <v>14367</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C116" s="4">
         <v>2</v>
@@ -2844,83 +2841,83 @@
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>14366</v>
+        <v>14928</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C117" s="4">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="D117" s="3">
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>14367</v>
+        <v>15405</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C118" s="4">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="D118" s="3">
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>14928</v>
+        <v>16460</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C119" s="4">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="D119" s="3">
         <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>15405</v>
+        <v>16461</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C120" s="4">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="D120" s="3">
         <v>12</v>
       </c>
       <c r="E120" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>16460</v>
+        <v>16462</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C121" s="4">
         <v>1</v>
@@ -2929,110 +2926,77 @@
         <v>12</v>
       </c>
       <c r="E121" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <v>16461</v>
+        <v>17075</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C122" s="4">
-        <v>1</v>
+        <v>5230</v>
       </c>
       <c r="D122" s="3">
         <v>12</v>
       </c>
       <c r="E122" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <v>16462</v>
+        <v>17076</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C123" s="4">
-        <v>1</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="D123" s="3">
         <v>12</v>
       </c>
       <c r="E123" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <v>17075</v>
+        <v>30189</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C124" s="4">
-        <v>640</v>
+        <v>500</v>
       </c>
       <c r="D124" s="3">
         <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="3">
-        <v>17075</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C125" s="4">
-        <v>5230</v>
-      </c>
-      <c r="D125" s="3">
-        <v>12</v>
-      </c>
-      <c r="E125" t="s">
-        <v>118</v>
-      </c>
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="3"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="3">
-        <v>17076</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C126" s="4">
-        <v>140.80000000000001</v>
-      </c>
-      <c r="D126" s="3">
-        <v>12</v>
-      </c>
-      <c r="E126" t="s">
-        <v>118</v>
-      </c>
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="3"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="3">
-        <v>30189</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C127" s="4">
-        <v>500</v>
-      </c>
-      <c r="D127" s="3">
-        <v>12</v>
-      </c>
-      <c r="E127" t="s">
-        <v>135</v>
-      </c>
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\TRANSFER-ANALISE-CORRIGIDO\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="14_{33D7B264-E024-46AE-875B-F5C883B9D1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{637C540A-A232-4A62-B3C2-95F04CAAD9D7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3575482-E300-4915-8560-DB6B9CF12721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="138">
   <si>
     <t>Produto</t>
   </si>
@@ -300,9 +300,6 @@
     <t>TRANSFER 59134 NEW</t>
   </si>
   <si>
-    <t>CARTEGE IRONING FILM 0,1MM</t>
-  </si>
-  <si>
     <t>TRASNFER LAMINA OT - PALAGI</t>
   </si>
   <si>
@@ -442,6 +439,18 @@
   </si>
   <si>
     <t>PROTECTION</t>
+  </si>
+  <si>
+    <t>TRANSFER PARCIAL EC150 FURTA COR 201 (NACIONAL)</t>
+  </si>
+  <si>
+    <t>TRANSFER PARC. MX911F - ROSE GOLD - UNIFOILS</t>
+  </si>
+  <si>
+    <t>TRANSFER MX905F - SALMAO CLARO</t>
+  </si>
+  <si>
+    <t>HOT STAMP PARCIAL ROSE 303</t>
   </si>
 </sst>
 </file>
@@ -883,10 +892,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -903,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -920,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -937,7 +946,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -954,7 +963,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -971,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -988,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1005,7 +1014,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1022,7 +1031,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,7 +1048,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1056,7 +1065,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,7 +1082,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1090,7 +1099,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1107,7 +1116,7 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1124,7 +1133,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1141,7 +1150,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1158,7 +1167,7 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1175,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1192,7 +1201,7 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1209,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1226,7 +1235,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1243,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1260,7 +1269,7 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1268,44 +1277,44 @@
         <v>4413</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2315</v>
+      </c>
+      <c r="D24" s="3">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
         <v>127</v>
-      </c>
-      <c r="C24" s="4">
-        <v>10.3</v>
-      </c>
-      <c r="D24" s="3">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>4413</v>
+        <v>4423</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4">
-        <v>2515</v>
+        <v>100</v>
       </c>
       <c r="D25" s="3">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>4423</v>
+        <v>4721</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4">
-        <v>100</v>
+        <v>1701.5</v>
       </c>
       <c r="D26" s="3">
         <v>12</v>
@@ -1316,81 +1325,81 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>4721</v>
+        <v>4722</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4">
-        <v>1701.5</v>
+        <v>3883.5</v>
       </c>
       <c r="D27" s="3">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>4722</v>
+        <v>4723</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4">
-        <v>3883.5</v>
+        <v>2974.5</v>
       </c>
       <c r="D28" s="3">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>4723</v>
+        <v>5024</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4">
-        <v>2974.5</v>
+        <v>3325.5</v>
       </c>
       <c r="D29" s="3">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>5024</v>
+        <v>5025</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="4">
-        <v>3325.5</v>
+        <v>3064.5</v>
       </c>
       <c r="D30" s="3">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>5025</v>
+        <v>5437</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31" s="4">
-        <v>3064.5</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3">
         <v>12</v>
@@ -1401,104 +1410,104 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>5437</v>
+        <v>5861</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C32" s="4">
-        <v>70</v>
+        <v>328</v>
       </c>
       <c r="D32" s="3">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>5861</v>
+        <v>5931</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4">
-        <v>328</v>
+        <v>11</v>
       </c>
       <c r="D33" s="3">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C34" s="4">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>5932</v>
+        <v>6248</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35" s="4">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="D35" s="3">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>6248</v>
+        <v>6560</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36" s="4">
-        <v>350</v>
+        <v>2083.5</v>
       </c>
       <c r="D36" s="3">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>6560</v>
+        <v>7425</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="4">
-        <v>2083.5</v>
+        <v>300</v>
       </c>
       <c r="D37" s="3">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1509,81 +1518,81 @@
         <v>37</v>
       </c>
       <c r="C38" s="4">
-        <v>300</v>
+        <v>7288.78</v>
       </c>
       <c r="D38" s="3">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>7425</v>
+        <v>7484</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="C39" s="4">
-        <v>7588.78</v>
+        <v>12572</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>7484</v>
+        <v>7485</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="C40" s="4">
-        <v>1272</v>
+        <v>2404.5</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>7485</v>
+        <v>7486</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" s="4">
-        <v>2404.5</v>
+        <v>15880.5</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>7486</v>
+        <v>7718</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="C42" s="4">
-        <v>15880.5</v>
+        <v>800</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1600,7 +1609,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1617,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1634,7 +1643,7 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1651,7 +1660,7 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1668,7 +1677,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1685,7 +1694,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1702,7 +1711,7 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1719,7 +1728,7 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1736,7 +1745,7 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1747,13 +1756,13 @@
         <v>49</v>
       </c>
       <c r="C52" s="4">
-        <v>528.5</v>
+        <v>0.5</v>
       </c>
       <c r="D52" s="3">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1770,7 +1779,7 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1787,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1804,7 +1813,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1821,7 +1830,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1838,7 +1847,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1855,7 +1864,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1872,7 +1881,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1889,7 +1898,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1906,7 +1915,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1923,7 +1932,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1940,7 +1949,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1957,7 +1966,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1974,7 +1983,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1991,7 +2000,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2008,7 +2017,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2025,7 +2034,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2042,7 +2051,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2059,7 +2068,7 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2076,7 +2085,7 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2093,7 +2102,7 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2110,7 +2119,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2118,16 +2127,16 @@
         <v>10090</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C74" s="4">
-        <v>7550</v>
+        <v>7235</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2144,7 +2153,7 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2161,7 +2170,7 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2178,7 +2187,7 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2195,7 +2204,7 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2212,7 +2221,7 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2229,7 +2238,7 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2246,7 +2255,7 @@
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2263,7 +2272,7 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2280,7 +2289,7 @@
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2297,7 +2306,7 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2314,7 +2323,7 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2331,7 +2340,7 @@
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2348,7 +2357,7 @@
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2365,7 +2374,7 @@
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2382,7 +2391,7 @@
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2399,7 +2408,7 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2416,7 +2425,7 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2433,7 +2442,7 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2450,29 +2459,29 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11243</v>
+        <v>11269</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C94" s="4">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="D94" s="3">
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11269</v>
+        <v>11316</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>88</v>
@@ -2484,109 +2493,109 @@
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11316</v>
+        <v>11318</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C96" s="4">
-        <v>10</v>
+        <v>97.7</v>
       </c>
       <c r="D96" s="3">
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11318</v>
+        <v>11362</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C97" s="4">
-        <v>97.7</v>
+        <v>5</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11362</v>
+        <v>11396</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C98" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D98" s="3">
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>11396</v>
+        <v>11397</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C99" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>11397</v>
+        <v>11444</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C100" s="4">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="D100" s="3">
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>11444</v>
+        <v>11866</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="C101" s="4">
-        <v>230</v>
+        <v>7.5</v>
       </c>
       <c r="D101" s="3">
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2594,7 +2603,7 @@
         <v>12497</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C102" s="4">
         <v>5</v>
@@ -2603,7 +2612,7 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2611,7 +2620,7 @@
         <v>12498</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C103" s="4">
         <v>5</v>
@@ -2620,7 +2629,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2628,7 +2637,7 @@
         <v>12499</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C104" s="4">
         <v>5</v>
@@ -2637,7 +2646,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2645,7 +2654,7 @@
         <v>12501</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C105" s="4">
         <v>5</v>
@@ -2654,7 +2663,7 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2662,7 +2671,7 @@
         <v>12503</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C106" s="4">
         <v>5</v>
@@ -2671,7 +2680,7 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2679,7 +2688,7 @@
         <v>12504</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
@@ -2688,7 +2697,7 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2696,16 +2705,16 @@
         <v>12514</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C108" s="4">
-        <v>1200.0999999999999</v>
+        <v>951.1</v>
       </c>
       <c r="D108" s="3">
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2713,16 +2722,16 @@
         <v>12515</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C109" s="4">
-        <v>5480</v>
+        <v>4680</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2730,7 +2739,7 @@
         <v>12516</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C110" s="4">
         <v>2364.6</v>
@@ -2739,7 +2748,7 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -2747,7 +2756,7 @@
         <v>12517</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C111" s="4">
         <v>740.4</v>
@@ -2756,7 +2765,7 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -2764,7 +2773,7 @@
         <v>12673</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C112" s="4">
         <v>5</v>
@@ -2773,7 +2782,7 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2781,7 +2790,7 @@
         <v>13150</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C113" s="4">
         <v>337.2</v>
@@ -2790,7 +2799,7 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2798,7 +2807,7 @@
         <v>14365</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C114" s="4">
         <v>2</v>
@@ -2807,7 +2816,7 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -2815,7 +2824,7 @@
         <v>14366</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C115" s="4">
         <v>2</v>
@@ -2824,7 +2833,7 @@
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -2832,7 +2841,7 @@
         <v>14367</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C116" s="4">
         <v>2</v>
@@ -2841,7 +2850,7 @@
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -2849,7 +2858,7 @@
         <v>14928</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C117" s="4">
         <v>7.5</v>
@@ -2858,7 +2867,7 @@
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -2866,7 +2875,7 @@
         <v>15405</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C118" s="4">
         <v>225</v>
@@ -2875,7 +2884,7 @@
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -2883,7 +2892,7 @@
         <v>16460</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C119" s="4">
         <v>1</v>
@@ -2892,7 +2901,7 @@
         <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -2900,7 +2909,7 @@
         <v>16461</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C120" s="4">
         <v>1</v>
@@ -2909,7 +2918,7 @@
         <v>12</v>
       </c>
       <c r="E120" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -2917,7 +2926,7 @@
         <v>16462</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C121" s="4">
         <v>1</v>
@@ -2926,7 +2935,7 @@
         <v>12</v>
       </c>
       <c r="E121" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -2934,16 +2943,16 @@
         <v>17075</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C122" s="4">
-        <v>5230</v>
+        <v>4830</v>
       </c>
       <c r="D122" s="3">
         <v>12</v>
       </c>
       <c r="E122" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -2951,7 +2960,7 @@
         <v>17076</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C123" s="4">
         <v>140.80000000000001</v>
@@ -2960,37 +2969,59 @@
         <v>12</v>
       </c>
       <c r="E123" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
+        <v>18237</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C124" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D124" s="3">
+        <v>12</v>
+      </c>
+      <c r="E124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="3">
+        <v>18245</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D125" s="3">
+        <v>12</v>
+      </c>
+      <c r="E125" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="3">
         <v>30189</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B126" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C126" s="4">
+        <v>500</v>
+      </c>
+      <c r="D126" s="3">
+        <v>12</v>
+      </c>
+      <c r="E126" t="s">
         <v>133</v>
       </c>
-      <c r="C124" s="4">
-        <v>500</v>
-      </c>
-      <c r="D124" s="3">
-        <v>12</v>
-      </c>
-      <c r="E124" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="3"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="3"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="3"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="3"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>

--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\TRANSFER-ANALISE-CORRIGIDO\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3575482-E300-4915-8560-DB6B9CF12721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7D1563-0119-47D2-8B4C-344264AD6553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="138">
   <si>
     <t>Produto</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Qtd.física</t>
   </si>
   <si>
-    <t>TRANSF PARC EC150 FURTA COR 201 - ECOTEX/MLT COL MOD 99-5 AM</t>
-  </si>
-  <si>
     <t>TRANSFER PARCIAL EC150 AZUL 014 - ECOTEX</t>
   </si>
   <si>
@@ -451,6 +448,9 @@
   </si>
   <si>
     <t>HOT STAMP PARCIAL ROSE 303</t>
+  </si>
+  <si>
+    <t>TRANSF PARC FURTA COR 201 - MOD 99-5 AM</t>
   </si>
 </sst>
 </file>
@@ -871,7 +871,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -892,10 +892,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -903,7 +903,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="C2" s="4">
         <v>27.5</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -920,7 +920,7 @@
         <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4">
         <v>495</v>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -937,7 +937,7 @@
         <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4">
         <v>2917</v>
@@ -946,7 +946,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
         <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4">
         <v>995</v>
@@ -963,7 +963,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -971,7 +971,7 @@
         <v>195</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4">
         <v>500</v>
@@ -980,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -988,7 +988,7 @@
         <v>204</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4">
         <v>2646</v>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1005,7 +1005,7 @@
         <v>381</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4">
         <v>4899.5</v>
@@ -1014,7 +1014,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1022,7 +1022,7 @@
         <v>383</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4">
         <v>200</v>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,7 +1039,7 @@
         <v>399</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4">
         <v>200</v>
@@ -1048,7 +1048,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1056,7 +1056,7 @@
         <v>1006</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4">
         <v>236</v>
@@ -1065,7 +1065,7 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,7 +1073,7 @@
         <v>1053</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4">
         <v>300</v>
@@ -1082,7 +1082,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1090,7 +1090,7 @@
         <v>2890</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4">
         <v>600</v>
@@ -1099,7 +1099,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1107,7 +1107,7 @@
         <v>2891</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4">
         <v>1489</v>
@@ -1116,7 +1116,7 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1124,7 +1124,7 @@
         <v>2905</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="4">
         <v>84</v>
@@ -1133,7 +1133,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1141,7 +1141,7 @@
         <v>3044</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="4">
         <v>544</v>
@@ -1150,7 +1150,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1158,7 +1158,7 @@
         <v>3109</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="4">
         <v>4832</v>
@@ -1167,7 +1167,7 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
         <v>3211</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4">
         <v>1950</v>
@@ -1184,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1192,7 +1192,7 @@
         <v>3495</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4">
         <v>2199</v>
@@ -1201,7 +1201,7 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1209,7 +1209,7 @@
         <v>4010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
         <v>491</v>
@@ -1218,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1226,7 +1226,7 @@
         <v>4067</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="4">
         <v>40</v>
@@ -1235,7 +1235,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1243,7 +1243,7 @@
         <v>4375</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
         <v>900</v>
@@ -1252,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1260,7 +1260,7 @@
         <v>4376</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="4">
         <v>2819</v>
@@ -1269,7 +1269,7 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1277,7 +1277,7 @@
         <v>4413</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24" s="4">
         <v>2315</v>
@@ -1286,7 +1286,7 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1294,7 +1294,7 @@
         <v>4423</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
         <v>100</v>
@@ -1303,7 +1303,7 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1311,7 +1311,7 @@
         <v>4721</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4">
         <v>1701.5</v>
@@ -1320,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1328,7 +1328,7 @@
         <v>4722</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4">
         <v>3883.5</v>
@@ -1337,7 +1337,7 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1345,7 +1345,7 @@
         <v>4723</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="4">
         <v>2974.5</v>
@@ -1354,7 +1354,7 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1362,16 +1362,16 @@
         <v>5024</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4">
-        <v>3325.5</v>
+        <v>3315.5</v>
       </c>
       <c r="D29" s="3">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1379,7 +1379,7 @@
         <v>5025</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="4">
         <v>3064.5</v>
@@ -1388,7 +1388,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1396,7 +1396,7 @@
         <v>5437</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="4">
         <v>70</v>
@@ -1405,7 +1405,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1413,7 +1413,7 @@
         <v>5861</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4">
         <v>328</v>
@@ -1422,7 +1422,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1430,7 +1430,7 @@
         <v>5931</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4">
         <v>11</v>
@@ -1439,7 +1439,7 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1447,7 +1447,7 @@
         <v>5932</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="4">
         <v>80</v>
@@ -1456,7 +1456,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1464,7 +1464,7 @@
         <v>6248</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="4">
         <v>350</v>
@@ -1473,7 +1473,7 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1481,7 +1481,7 @@
         <v>6560</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="4">
         <v>2083.5</v>
@@ -1490,7 +1490,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1498,7 +1498,7 @@
         <v>7425</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="4">
         <v>300</v>
@@ -1507,7 +1507,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1515,7 +1515,7 @@
         <v>7425</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="4">
         <v>7288.78</v>
@@ -1524,7 +1524,7 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1532,95 +1532,95 @@
         <v>7484</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C39" s="4">
-        <v>12572</v>
+        <v>6972</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="C40" s="4">
-        <v>2404.5</v>
+        <v>8800</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>7486</v>
+        <v>7485</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="4">
-        <v>15880.5</v>
+        <v>2404.5</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>7718</v>
+        <v>7485</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C42" s="4">
-        <v>800</v>
+        <v>6000</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>7771</v>
+        <v>7486</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C43" s="4">
-        <v>1191</v>
+        <v>15880.5</v>
       </c>
       <c r="D43" s="3">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>8111</v>
+        <v>7718</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="C44" s="4">
-        <v>383</v>
+        <v>800</v>
       </c>
       <c r="D44" s="3">
         <v>12</v>
@@ -1631,639 +1631,639 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>8175</v>
+        <v>7771</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C45" s="4">
-        <v>2377.5</v>
+        <v>1191</v>
       </c>
       <c r="D45" s="3">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>8418</v>
+        <v>8111</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C46" s="4">
-        <v>954.5</v>
+        <v>383</v>
       </c>
       <c r="D46" s="3">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>8472</v>
+        <v>8175</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C47" s="4">
-        <v>10</v>
+        <v>2377.5</v>
       </c>
       <c r="D47" s="3">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>8612</v>
+        <v>8418</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C48" s="4">
-        <v>600</v>
+        <v>954.5</v>
       </c>
       <c r="D48" s="3">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>8613</v>
+        <v>8472</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C49" s="4">
-        <v>410</v>
+        <v>10</v>
       </c>
       <c r="D49" s="3">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>8645</v>
+        <v>8612</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C50" s="4">
-        <v>35</v>
+        <v>600</v>
       </c>
       <c r="D50" s="3">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>8713</v>
+        <v>8613</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C51" s="4">
-        <v>463</v>
+        <v>410</v>
       </c>
       <c r="D51" s="3">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>9000</v>
+        <v>8645</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C52" s="4">
-        <v>0.5</v>
+        <v>35</v>
       </c>
       <c r="D52" s="3">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>9009</v>
+        <v>8713</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C53" s="4">
-        <v>60</v>
+        <v>463</v>
       </c>
       <c r="D53" s="3">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>9336</v>
+        <v>9000</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C54" s="4">
-        <v>750.1</v>
+        <v>0.5</v>
       </c>
       <c r="D54" s="3">
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>9396</v>
+        <v>9009</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C55" s="4">
-        <v>125.5</v>
+        <v>60</v>
       </c>
       <c r="D55" s="3">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>9397</v>
+        <v>9336</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C56" s="4">
-        <v>1299</v>
+        <v>571.29999999999995</v>
       </c>
       <c r="D56" s="3">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>9398</v>
+        <v>9396</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C57" s="4">
-        <v>1199</v>
+        <v>125.5</v>
       </c>
       <c r="D57" s="3">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>9399</v>
+        <v>9397</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C58" s="4">
-        <v>594</v>
+        <v>1299</v>
       </c>
       <c r="D58" s="3">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>9430</v>
+        <v>9398</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C59" s="4">
-        <v>25</v>
+        <v>1199</v>
       </c>
       <c r="D59" s="3">
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>9430</v>
+        <v>9399</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C60" s="4">
-        <v>2327.8000000000002</v>
+        <v>594</v>
       </c>
       <c r="D60" s="3">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>9476</v>
+        <v>9430</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C61" s="4">
-        <v>1768.5</v>
+        <v>25</v>
       </c>
       <c r="D61" s="3">
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>9591</v>
+        <v>9430</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C62" s="4">
-        <v>5</v>
+        <v>2327.8000000000002</v>
       </c>
       <c r="D62" s="3">
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>9633</v>
+        <v>9476</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C63" s="4">
-        <v>400</v>
+        <v>1768.5</v>
       </c>
       <c r="D63" s="3">
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>9804</v>
+        <v>9591</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C64" s="4">
-        <v>1058</v>
+        <v>5</v>
       </c>
       <c r="D64" s="3">
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>9805</v>
+        <v>9633</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C65" s="4">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="D65" s="3">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>10026</v>
+        <v>9804</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C66" s="4">
-        <v>5</v>
+        <v>1058</v>
       </c>
       <c r="D66" s="3">
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>10027</v>
+        <v>9805</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C67" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D67" s="3">
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>10028</v>
+        <v>10026</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C68" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68" s="3">
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>10031</v>
+        <v>10027</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C69" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D69" s="3">
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>10042</v>
+        <v>10028</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C70" s="4">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D70" s="3">
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>10042</v>
+        <v>10031</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C71" s="4">
-        <v>945</v>
+        <v>15</v>
       </c>
       <c r="D71" s="3">
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>10044</v>
+        <v>10042</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C72" s="4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D72" s="3">
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>10080</v>
+        <v>10042</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C73" s="4">
-        <v>50</v>
+        <v>945</v>
       </c>
       <c r="D73" s="3">
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>10090</v>
+        <v>10044</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="C74" s="4">
-        <v>7235</v>
+        <v>80</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>10254</v>
+        <v>10080</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C75" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D75" s="3">
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>10318</v>
+        <v>10090</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="C76" s="4">
-        <v>50</v>
+        <v>3200</v>
       </c>
       <c r="D76" s="3">
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>10362</v>
+        <v>10090</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="C77" s="4">
-        <v>10</v>
+        <v>7235</v>
       </c>
       <c r="D77" s="3">
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>10692</v>
+        <v>10254</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C78" s="4">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D78" s="3">
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>10707</v>
+        <v>10318</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C79" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D79" s="3">
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>10725</v>
+        <v>10362</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C80" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D80" s="3">
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>10762</v>
+        <v>10692</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C81" s="4">
-        <v>1376.8</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3">
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>10830</v>
+        <v>10707</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C82" s="4">
         <v>3</v>
@@ -2272,185 +2272,185 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>10832</v>
+        <v>10725</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C83" s="4">
-        <v>1015</v>
+        <v>3</v>
       </c>
       <c r="D83" s="3">
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>10834</v>
+        <v>10762</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C84" s="4">
-        <v>5</v>
+        <v>1376.8</v>
       </c>
       <c r="D84" s="3">
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>10836</v>
+        <v>10830</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C85" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D85" s="3">
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>10936</v>
+        <v>10832</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C86" s="4">
-        <v>1093.3499999999999</v>
+        <v>1015</v>
       </c>
       <c r="D86" s="3">
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>10937</v>
+        <v>10834</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C87" s="4">
-        <v>1183.5</v>
+        <v>5</v>
       </c>
       <c r="D87" s="3">
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>10997</v>
+        <v>10836</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C88" s="4">
-        <v>188.5</v>
+        <v>5</v>
       </c>
       <c r="D88" s="3">
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>10998</v>
+        <v>10936</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C89" s="4">
-        <v>69.352999999999994</v>
+        <v>1093.3499999999999</v>
       </c>
       <c r="D89" s="3">
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>11003</v>
+        <v>10937</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C90" s="4">
-        <v>5</v>
+        <v>1183.5</v>
       </c>
       <c r="D90" s="3">
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>11105</v>
+        <v>10997</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C91" s="4">
-        <v>5</v>
+        <v>188.5</v>
       </c>
       <c r="D91" s="3">
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>11106</v>
+        <v>10998</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C92" s="4">
-        <v>20</v>
+        <v>69.352999999999994</v>
       </c>
       <c r="D92" s="3">
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>11107</v>
+        <v>11003</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C93" s="4">
         <v>5</v>
@@ -2459,151 +2459,151 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11269</v>
+        <v>11105</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C94" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D94" s="3">
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11316</v>
+        <v>11106</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C95" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11318</v>
+        <v>11107</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C96" s="4">
-        <v>97.7</v>
+        <v>5</v>
       </c>
       <c r="D96" s="3">
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11362</v>
+        <v>11269</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C97" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11396</v>
+        <v>11316</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C98" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D98" s="3">
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>11397</v>
+        <v>11318</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C99" s="4">
-        <v>5</v>
+        <v>97.7</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>11444</v>
+        <v>11362</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C100" s="4">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="D100" s="3">
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>11866</v>
+        <v>11396</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="C101" s="4">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D101" s="3">
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>12497</v>
+        <v>11397</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C102" s="4">
         <v>5</v>
@@ -2612,49 +2612,49 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>12498</v>
+        <v>11444</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C103" s="4">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="D103" s="3">
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>12499</v>
+        <v>11866</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C104" s="4">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D104" s="3">
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>12501</v>
+        <v>12497</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C105" s="4">
         <v>5</v>
@@ -2663,15 +2663,15 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>12503</v>
+        <v>12498</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C106" s="4">
         <v>5</v>
@@ -2680,15 +2680,15 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>12504</v>
+        <v>12499</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
@@ -2697,18 +2697,18 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>12514</v>
+        <v>12501</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C108" s="4">
-        <v>951.1</v>
+        <v>5</v>
       </c>
       <c r="D108" s="3">
         <v>12</v>
@@ -2719,30 +2719,30 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>12515</v>
+        <v>12503</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="C109" s="4">
-        <v>4680</v>
+        <v>5</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>12516</v>
+        <v>12504</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C110" s="4">
-        <v>2364.6</v>
+        <v>5</v>
       </c>
       <c r="D110" s="3">
         <v>12</v>
@@ -2753,281 +2753,326 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>12517</v>
+        <v>12514</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C111" s="4">
-        <v>740.4</v>
+        <v>951.1</v>
       </c>
       <c r="D111" s="3">
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>12673</v>
+        <v>12515</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C112" s="4">
-        <v>5</v>
+        <v>3905.2</v>
       </c>
       <c r="D112" s="3">
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>13150</v>
+        <v>12516</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C113" s="4">
-        <v>337.2</v>
+        <v>2364.6</v>
       </c>
       <c r="D113" s="3">
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>14365</v>
+        <v>12517</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C114" s="4">
-        <v>2</v>
+        <v>636.4</v>
       </c>
       <c r="D114" s="3">
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>14366</v>
+        <v>12673</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C115" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D115" s="3">
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>14367</v>
+        <v>13150</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C116" s="4">
-        <v>2</v>
+        <v>337.2</v>
       </c>
       <c r="D116" s="3">
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>14928</v>
+        <v>14365</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C117" s="4">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="D117" s="3">
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>15405</v>
+        <v>14366</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C118" s="4">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="D118" s="3">
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>16460</v>
+        <v>14367</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C119" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="3">
         <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>16461</v>
+        <v>14928</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C120" s="4">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="D120" s="3">
         <v>12</v>
       </c>
       <c r="E120" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>16462</v>
+        <v>15405</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C121" s="4">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="D121" s="3">
         <v>12</v>
       </c>
       <c r="E121" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <v>17075</v>
+        <v>16460</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C122" s="4">
-        <v>4830</v>
+        <v>1</v>
       </c>
       <c r="D122" s="3">
         <v>12</v>
       </c>
       <c r="E122" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <v>17076</v>
+        <v>16461</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C123" s="4">
-        <v>140.80000000000001</v>
+        <v>1</v>
       </c>
       <c r="D123" s="3">
         <v>12</v>
       </c>
       <c r="E123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <v>18237</v>
+        <v>16462</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="C124" s="4">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3">
         <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <v>18245</v>
+        <v>17075</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C125" s="4">
-        <v>1000</v>
+        <v>4830</v>
       </c>
       <c r="D125" s="3">
         <v>12</v>
       </c>
       <c r="E125" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
+        <v>17076</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C126" s="4">
+        <v>3070</v>
+      </c>
+      <c r="D126" s="3">
+        <v>12</v>
+      </c>
+      <c r="E126" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="3">
+        <v>18237</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C127" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D127" s="3">
+        <v>12</v>
+      </c>
+      <c r="E127" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="3">
+        <v>18245</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C128" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D128" s="3">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="3">
         <v>30189</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B129" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C129" s="4">
+        <v>500</v>
+      </c>
+      <c r="D129" s="3">
+        <v>12</v>
+      </c>
+      <c r="E129" t="s">
         <v>132</v>
       </c>
-      <c r="C126" s="4">
-        <v>500</v>
-      </c>
-      <c r="D126" s="3">
-        <v>12</v>
-      </c>
-      <c r="E126" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="3"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data-source/ESTOQUETRANSFER.xlsx
+++ b/data-source/ESTOQUETRANSFER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\TRANSFER-ANALISE-CORRIGIDO\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7D1563-0119-47D2-8B4C-344264AD6553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0FC897-BE68-44BF-82EF-FE21B6557289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="138">
   <si>
     <t>Produto</t>
   </si>
@@ -474,6 +474,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1280,7 +1281,7 @@
         <v>125</v>
       </c>
       <c r="C24" s="4">
-        <v>2315</v>
+        <v>2134</v>
       </c>
       <c r="D24" s="3">
         <v>12</v>
@@ -1518,7 +1519,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="4">
-        <v>7288.78</v>
+        <v>6888.78</v>
       </c>
       <c r="D38" s="3">
         <v>12</v>
@@ -1535,7 +1536,7 @@
         <v>127</v>
       </c>
       <c r="C39" s="4">
-        <v>6972</v>
+        <v>9458</v>
       </c>
       <c r="D39" s="3">
         <v>12</v>
@@ -1546,13 +1547,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>7484</v>
+        <v>7485</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="C40" s="4">
-        <v>8800</v>
+        <v>5000</v>
       </c>
       <c r="D40" s="3">
         <v>12</v>
@@ -1569,7 +1570,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="4">
-        <v>2404.5</v>
+        <v>7404.5</v>
       </c>
       <c r="D41" s="3">
         <v>12</v>
@@ -1580,13 +1581,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>7485</v>
+        <v>7486</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42" s="4">
-        <v>6000</v>
+        <v>15880.5</v>
       </c>
       <c r="D42" s="3">
         <v>12</v>
@@ -1597,81 +1598,81 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>7486</v>
+        <v>7718</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="C43" s="4">
-        <v>15880.5</v>
+        <v>800</v>
       </c>
       <c r="D43" s="3">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>7718</v>
+        <v>7771</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="C44" s="4">
-        <v>800</v>
+        <v>1191</v>
       </c>
       <c r="D44" s="3">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>7771</v>
+        <v>8111</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C45" s="4">
-        <v>1191</v>
+        <v>373</v>
       </c>
       <c r="D45" s="3">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>8111</v>
+        <v>8175</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C46" s="4">
-        <v>383</v>
+        <v>2377.5</v>
       </c>
       <c r="D46" s="3">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>8175</v>
+        <v>8418</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47" s="4">
-        <v>2377.5</v>
+        <v>954.5</v>
       </c>
       <c r="D47" s="3">
         <v>12</v>
@@ -1682,47 +1683,47 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>8418</v>
+        <v>8472</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C48" s="4">
-        <v>954.5</v>
+        <v>10</v>
       </c>
       <c r="D48" s="3">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>8472</v>
+        <v>8612</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C49" s="4">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="D49" s="3">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>8612</v>
+        <v>8613</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4">
-        <v>600</v>
+        <v>410</v>
       </c>
       <c r="D50" s="3">
         <v>12</v>
@@ -1733,13 +1734,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>8613</v>
+        <v>8645</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C51" s="4">
-        <v>410</v>
+        <v>35</v>
       </c>
       <c r="D51" s="3">
         <v>12</v>
@@ -1750,98 +1751,98 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>8645</v>
+        <v>8713</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C52" s="4">
-        <v>35</v>
+        <v>463</v>
       </c>
       <c r="D52" s="3">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>8713</v>
+        <v>9000</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C53" s="4">
-        <v>463</v>
+        <v>0.5</v>
       </c>
       <c r="D53" s="3">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>9000</v>
+        <v>9009</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" s="4">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D54" s="3">
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>9009</v>
+        <v>9336</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C55" s="4">
-        <v>60</v>
+        <v>571.29999999999995</v>
       </c>
       <c r="D55" s="3">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>9336</v>
+        <v>9396</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C56" s="4">
-        <v>571.29999999999995</v>
+        <v>125.5</v>
       </c>
       <c r="D56" s="3">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>9396</v>
+        <v>9397</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C57" s="4">
-        <v>125.5</v>
+        <v>1299</v>
       </c>
       <c r="D57" s="3">
         <v>12</v>
@@ -1852,13 +1853,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>9397</v>
+        <v>9398</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C58" s="4">
-        <v>1299</v>
+        <v>1199</v>
       </c>
       <c r="D58" s="3">
         <v>12</v>
@@ -1869,13 +1870,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>9398</v>
+        <v>9399</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C59" s="4">
-        <v>1199</v>
+        <v>394</v>
       </c>
       <c r="D59" s="3">
         <v>12</v>
@@ -1886,19 +1887,19 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>9399</v>
+        <v>9430</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C60" s="4">
-        <v>594</v>
+        <v>25</v>
       </c>
       <c r="D60" s="3">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1909,7 +1910,7 @@
         <v>55</v>
       </c>
       <c r="C61" s="4">
-        <v>25</v>
+        <v>2327.8000000000002</v>
       </c>
       <c r="D61" s="3">
         <v>12</v>
@@ -1920,13 +1921,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>9430</v>
+        <v>9476</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C62" s="4">
-        <v>2327.8000000000002</v>
+        <v>1768.5</v>
       </c>
       <c r="D62" s="3">
         <v>12</v>
@@ -1937,13 +1938,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>9476</v>
+        <v>9591</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C63" s="4">
-        <v>1768.5</v>
+        <v>5</v>
       </c>
       <c r="D63" s="3">
         <v>12</v>
@@ -1954,13 +1955,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>9591</v>
+        <v>9633</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C64" s="4">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="D64" s="3">
         <v>12</v>
@@ -1971,13 +1972,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>9633</v>
+        <v>9804</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C65" s="4">
-        <v>400</v>
+        <v>1058</v>
       </c>
       <c r="D65" s="3">
         <v>12</v>
@@ -1988,13 +1989,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>9804</v>
+        <v>9805</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C66" s="4">
-        <v>1058</v>
+        <v>40</v>
       </c>
       <c r="D66" s="3">
         <v>12</v>
@@ -2005,13 +2006,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>9805</v>
+        <v>10026</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C67" s="4">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D67" s="3">
         <v>12</v>
@@ -2022,10 +2023,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>10026</v>
+        <v>10027</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C68" s="4">
         <v>5</v>
@@ -2039,13 +2040,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>10027</v>
+        <v>10028</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C69" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D69" s="3">
         <v>12</v>
@@ -2056,13 +2057,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>10028</v>
+        <v>10031</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C70" s="4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D70" s="3">
         <v>12</v>
@@ -2073,13 +2074,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>10031</v>
+        <v>10042</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C71" s="4">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D71" s="3">
         <v>12</v>
@@ -2096,7 +2097,7 @@
         <v>65</v>
       </c>
       <c r="C72" s="4">
-        <v>100</v>
+        <v>945</v>
       </c>
       <c r="D72" s="3">
         <v>12</v>
@@ -2107,13 +2108,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>10042</v>
+        <v>10044</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C73" s="4">
-        <v>945</v>
+        <v>80</v>
       </c>
       <c r="D73" s="3">
         <v>12</v>
@@ -2124,13 +2125,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>10044</v>
+        <v>10080</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C74" s="4">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D74" s="3">
         <v>12</v>
@@ -2141,64 +2142,64 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>10080</v>
+        <v>10090</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="C75" s="4">
-        <v>50</v>
+        <v>10435</v>
       </c>
       <c r="D75" s="3">
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>10090</v>
+        <v>10254</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="C76" s="4">
-        <v>3200</v>
+        <v>70</v>
       </c>
       <c r="D76" s="3">
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>10090</v>
+        <v>10318</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="C77" s="4">
-        <v>7235</v>
+        <v>50</v>
       </c>
       <c r="D77" s="3">
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>10254</v>
+        <v>10362</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C78" s="4">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D78" s="3">
         <v>12</v>
@@ -2209,30 +2210,30 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>10318</v>
+        <v>10692</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C79" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D79" s="3">
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>10362</v>
+        <v>10707</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C80" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
         <v>12</v>
@@ -2243,10 +2244,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>10692</v>
+        <v>10725</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C81" s="4">
         <v>3</v>
@@ -2260,27 +2261,27 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>10707</v>
+        <v>10762</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C82" s="4">
-        <v>3</v>
+        <v>1376.8</v>
       </c>
       <c r="D82" s="3">
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>10725</v>
+        <v>10830</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C83" s="4">
         <v>3</v>
@@ -2294,47 +2295,47 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>10762</v>
+        <v>10832</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C84" s="4">
-        <v>1376.8</v>
+        <v>1015</v>
       </c>
       <c r="D84" s="3">
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>10830</v>
+        <v>10834</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C85" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D85" s="3">
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>10832</v>
+        <v>10836</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C86" s="4">
-        <v>1015</v>
+        <v>5</v>
       </c>
       <c r="D86" s="3">
         <v>12</v>
@@ -2345,13 +2346,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>10834</v>
+        <v>10936</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C87" s="4">
-        <v>5</v>
+        <v>1093.3499999999999</v>
       </c>
       <c r="D87" s="3">
         <v>12</v>
@@ -2362,13 +2363,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>10836</v>
+        <v>10937</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C88" s="4">
-        <v>5</v>
+        <v>1183.5</v>
       </c>
       <c r="D88" s="3">
         <v>12</v>
@@ -2379,13 +2380,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>10936</v>
+        <v>10997</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C89" s="4">
-        <v>1093.3499999999999</v>
+        <v>188.5</v>
       </c>
       <c r="D89" s="3">
         <v>12</v>
@@ -2396,13 +2397,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>10937</v>
+        <v>10998</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C90" s="4">
-        <v>1183.5</v>
+        <v>69.352999999999994</v>
       </c>
       <c r="D90" s="3">
         <v>12</v>
@@ -2413,13 +2414,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>10997</v>
+        <v>11003</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C91" s="4">
-        <v>188.5</v>
+        <v>5</v>
       </c>
       <c r="D91" s="3">
         <v>12</v>
@@ -2430,13 +2431,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>10998</v>
+        <v>11105</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C92" s="4">
-        <v>69.352999999999994</v>
+        <v>5</v>
       </c>
       <c r="D92" s="3">
         <v>12</v>
@@ -2447,13 +2448,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>11003</v>
+        <v>11106</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C93" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D93" s="3">
         <v>12</v>
@@ -2464,10 +2465,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>11105</v>
+        <v>11107</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C94" s="4">
         <v>5</v>
@@ -2481,13 +2482,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>11106</v>
+        <v>11269</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C95" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
@@ -2498,13 +2499,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>11107</v>
+        <v>11316</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C96" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D96" s="3">
         <v>12</v>
@@ -2515,13 +2516,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>11269</v>
+        <v>11318</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C97" s="4">
-        <v>10</v>
+        <v>97.7</v>
       </c>
       <c r="D97" s="3">
         <v>12</v>
@@ -2532,13 +2533,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>11316</v>
+        <v>11362</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C98" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D98" s="3">
         <v>12</v>
@@ -2549,13 +2550,13 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>11318</v>
+        <v>11396</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C99" s="4">
-        <v>97.7</v>
+        <v>7</v>
       </c>
       <c r="D99" s="3">
         <v>12</v>
@@ -2566,10 +2567,10 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>11362</v>
+        <v>11397</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C100" s="4">
         <v>5</v>
@@ -2583,13 +2584,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>11396</v>
+        <v>11444</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C101" s="4">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="D101" s="3">
         <v>12</v>
@@ -2600,13 +2601,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>11397</v>
+        <v>11866</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="C102" s="4">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D102" s="3">
         <v>12</v>
@@ -2617,30 +2618,30 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>11444</v>
+        <v>12497</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C103" s="4">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="D103" s="3">
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>11866</v>
+        <v>12498</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C104" s="4">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D104" s="3">
         <v>12</v>
@@ -2651,10 +2652,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>12497</v>
+        <v>12499</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C105" s="4">
         <v>5</v>
@@ -2663,15 +2664,15 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>12498</v>
+        <v>12501</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C106" s="4">
         <v>5</v>
@@ -2685,10 +2686,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>12499</v>
+        <v>12503</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
@@ -2697,15 +2698,15 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>12501</v>
+        <v>12504</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C108" s="4">
         <v>5</v>
@@ -2719,47 +2720,47 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>12503</v>
+        <v>12514</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C109" s="4">
-        <v>5</v>
+        <v>551.1</v>
       </c>
       <c r="D109" s="3">
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>12504</v>
+        <v>12515</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C110" s="4">
-        <v>5</v>
+        <v>3483.4609999999998</v>
       </c>
       <c r="D110" s="3">
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>12514</v>
+        <v>12516</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C111" s="4">
-        <v>951.1</v>
+        <v>2364.6</v>
       </c>
       <c r="D111" s="3">
         <v>12</v>
@@ -2770,13 +2771,13 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>12515</v>
+        <v>12517</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="C112" s="4">
-        <v>3905.2</v>
+        <v>636.4</v>
       </c>
       <c r="D112" s="3">
         <v>12</v>
@@ -2787,30 +2788,30 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>12516</v>
+        <v>12673</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C113" s="4">
-        <v>2364.6</v>
+        <v>5</v>
       </c>
       <c r="D113" s="3">
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>12517</v>
+        <v>13150</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C114" s="4">
-        <v>636.4</v>
+        <v>337.2</v>
       </c>
       <c r="D114" s="3">
         <v>12</v>
@@ -2821,13 +2822,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>12673</v>
+        <v>14365</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C115" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D115" s="3">
         <v>12</v>
@@ -2838,27 +2839,27 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>13150</v>
+        <v>14366</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C116" s="4">
-        <v>337.2</v>
+        <v>2</v>
       </c>
       <c r="D116" s="3">
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>14365</v>
+        <v>14367</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C117" s="4">
         <v>2</v>
@@ -2867,18 +2868,18 @@
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>14366</v>
+        <v>14928</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C118" s="4">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="D118" s="3">
         <v>12</v>
@@ -2889,13 +2890,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>14367</v>
+        <v>15405</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C119" s="4">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="D119" s="3">
         <v>12</v>
@@ -2906,30 +2907,30 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>14928</v>
+        <v>16460</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C120" s="4">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="D120" s="3">
         <v>12</v>
       </c>
       <c r="E120" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>15405</v>
+        <v>16461</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C121" s="4">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="D121" s="3">
         <v>12</v>
@@ -2940,10 +2941,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <v>16460</v>
+        <v>16462</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C122" s="4">
         <v>1</v>
@@ -2957,122 +2958,100 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <v>16461</v>
+        <v>17075</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C123" s="4">
-        <v>1</v>
+        <v>3790</v>
       </c>
       <c r="D123" s="3">
         <v>12</v>
       </c>
       <c r="E123" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <v>16462</v>
+        <v>17076</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C124" s="4">
-        <v>1</v>
+        <v>2870</v>
       </c>
       <c r="D124" s="3">
         <v>12</v>
       </c>
       <c r="E124" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <v>17075</v>
+        <v>18237</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C125" s="4">
-        <v>4830</v>
+        <v>7.5</v>
       </c>
       <c r="D125" s="3">
         <v>12</v>
       </c>
       <c r="E125" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
-        <v>17076</v>
+        <v>18245</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C126" s="4">
-        <v>3070</v>
+        <v>1000</v>
       </c>
       <c r="D126" s="3">
         <v>12</v>
       </c>
       <c r="E126" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
-        <v>18237</v>
+        <v>30189</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C127" s="4">
-        <v>7.5</v>
+        <v>500</v>
       </c>
       <c r="D127" s="3">
         <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="3">
-        <v>18245</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C128" s="4">
-        <v>1000</v>
-      </c>
-      <c r="D128" s="3">
-        <v>12</v>
-      </c>
-      <c r="E128" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="3">
-        <v>30189</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C129" s="4">
-        <v>500</v>
-      </c>
-      <c r="D129" s="3">
-        <v>12</v>
-      </c>
-      <c r="E129" t="s">
-        <v>132</v>
-      </c>
+      <c r="A128" s="3"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="3"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="3"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
